--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfoTemplate.xlsx
@@ -1068,6 +1068,24 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576 G2:G1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900000</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576 L2:L1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfoTemplate.xlsx
@@ -16,22 +16,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>退款单号</t>
-  </si>
-  <si>
-    <t>平台订单编号</t>
-  </si>
-  <si>
-    <t>平台名称</t>
-  </si>
-  <si>
-    <t>店铺名称</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>退款金额</t>
+    <t>*退款单号</t>
+  </si>
+  <si>
+    <t>*平台订单编号</t>
+  </si>
+  <si>
+    <t>*平台名称</t>
+  </si>
+  <si>
+    <t>*店铺名称</t>
+  </si>
+  <si>
+    <t>*SKU</t>
+  </si>
+  <si>
+    <t>*退款金额</t>
   </si>
   <si>
     <t>汇率</t>
@@ -40,16 +40,16 @@
     <t>结算汇率</t>
   </si>
   <si>
-    <t>退款数量</t>
-  </si>
-  <si>
-    <t>退款状态</t>
-  </si>
-  <si>
-    <t>退款时间</t>
-  </si>
-  <si>
-    <t>原订单时间</t>
+    <t>*退款数量</t>
+  </si>
+  <si>
+    <t>*退款状态</t>
+  </si>
+  <si>
+    <t>*退款时间</t>
+  </si>
+  <si>
+    <t>*币种</t>
   </si>
   <si>
     <t>错误信息</t>
@@ -1068,7 +1068,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900000</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576 G2:G1048576">
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
@@ -1077,11 +1081,10 @@
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900000</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"新建退款,审核中,财务审核,成功,失败,作废"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576 L2:L1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpRefundInfoTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>*退款单号</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>*币种</t>
-  </si>
-  <si>
-    <t>错误信息</t>
   </si>
 </sst>
 </file>
@@ -1023,10 +1020,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:13">
+    <row r="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,9 +1059,6 @@
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
